--- a/Imp/小鬼落点/落点结论.xlsx
+++ b/Imp/小鬼落点/落点结论.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17775" activeTab="1"/>
+    <workbookView windowWidth="20130" windowHeight="18915"/>
   </bookViews>
   <sheets>
     <sheet name="原始" sheetId="1" r:id="rId1"/>
     <sheet name="右侧南瓜" sheetId="2" r:id="rId2"/>
+    <sheet name="鬼盲" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="33">
   <si>
     <t>场地</t>
   </si>
@@ -104,6 +105,30 @@
   <si>
     <t>*炮尾*(</t>
   </si>
+  <si>
+    <t>鬼盲落点左(int)</t>
+  </si>
+  <si>
+    <t>鬼盲落点右(int)</t>
+  </si>
+  <si>
+    <t>巨人坐标左鬼盲(float)</t>
+  </si>
+  <si>
+    <t>巨人坐标右鬼盲(float)</t>
+  </si>
+  <si>
+    <t>普</t>
+  </si>
+  <si>
+    <t>曾</t>
+  </si>
+  <si>
+    <t>喷</t>
+  </si>
+  <si>
+    <t>刺</t>
+  </si>
 </sst>
 </file>
 
@@ -126,15 +151,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -747,22 +772,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1118,1747 +1148,1747 @@
     <col min="1" max="2" width="5.375" customWidth="1"/>
     <col min="3" max="3" width="7.125" customWidth="1"/>
     <col min="4" max="5" width="17.75" customWidth="1"/>
-    <col min="6" max="7" width="20.25" style="1" customWidth="1"/>
-    <col min="8" max="9" width="11.5" style="2" customWidth="1"/>
+    <col min="6" max="7" width="20.25" style="4" customWidth="1"/>
+    <col min="8" max="9" width="11.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="9">
+      <c r="A2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="12">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="12">
         <v>80</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="12">
         <v>120</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="13">
         <v>426</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="13">
         <v>553.9999389648</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="14">
         <v>3.75</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="A3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="12">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="12">
         <v>160</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="12">
         <v>200</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="13">
         <v>500.0000305176</v>
       </c>
-      <c r="G3" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H3" s="11">
+      <c r="G3" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H3" s="14">
         <v>4.675</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="A4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="12">
         <v>4</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="12">
         <v>240</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="12">
         <v>280</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="13">
         <v>727</v>
       </c>
-      <c r="G4" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H4" s="11">
+      <c r="G4" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H4" s="14">
         <v>7.5125</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="12">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="12">
         <v>-10</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="12">
         <v>70</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="13">
         <v>407.9999694824</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="14">
         <v>3.425</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="14">
         <v>7.975</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="9">
+      <c r="A6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="12">
         <v>-10</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="12">
         <v>69</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="13">
         <v>406.9999694824</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="14">
         <v>3.425</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="14">
         <v>7.9625</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="9">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="12">
         <v>2</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="12">
         <v>70</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="12">
         <v>150</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="13">
         <v>404</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="13">
         <v>700.9999389648</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="14">
         <v>3.475</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="9">
+      <c r="A8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="12">
         <v>2</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="12">
         <v>70</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="12">
         <v>149</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="13">
         <v>404</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="13">
         <v>696.9999389648</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="14">
         <v>3.475</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="9">
+      <c r="A9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="12">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="12">
         <v>71</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="12">
         <v>150</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="13">
         <v>405</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="13">
         <v>700.9999389648</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="14">
         <v>3.4875</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9">
+      <c r="A10" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12">
         <v>2</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="12">
         <v>71</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="12">
         <v>149</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="13">
         <v>405</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="13">
         <v>696.9999389648</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="14">
         <v>3.4875</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="9">
+      <c r="A11" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12">
         <v>3</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="12">
         <v>150</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="12">
         <v>230</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="13">
         <v>500.0000305176</v>
       </c>
-      <c r="G11" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H11" s="11">
+      <c r="G11" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H11" s="14">
         <v>4.675</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="9">
+      <c r="A12" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="12">
         <v>3</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="12">
         <v>150</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="12">
         <v>229</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="13">
         <v>500.0000305176</v>
       </c>
-      <c r="G12" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H12" s="11">
+      <c r="G12" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H12" s="14">
         <v>4.675</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="9">
+      <c r="A13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12">
         <v>3</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="12">
         <v>151</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="12">
         <v>230</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="13">
         <v>500.0000305176</v>
       </c>
-      <c r="G13" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H13" s="11">
+      <c r="G13" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H13" s="14">
         <v>4.675</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="9">
+      <c r="A14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="12">
         <v>3</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="12">
         <v>151</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="12">
         <v>229</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="13">
         <v>500.0000305176</v>
       </c>
-      <c r="G14" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H14" s="11">
+      <c r="G14" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H14" s="14">
         <v>4.675</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="9">
+      <c r="A15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="12">
         <v>4</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="12">
         <v>230</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="12">
         <v>310</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="13">
         <v>681</v>
       </c>
-      <c r="G15" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H15" s="11">
+      <c r="G15" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H15" s="14">
         <v>6.9375</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="9">
+      <c r="A16" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="12">
         <v>4</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="12">
         <v>230</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="12">
         <v>309</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="13">
         <v>681</v>
       </c>
-      <c r="G16" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H16" s="11">
+      <c r="G16" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H16" s="14">
         <v>6.9375</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="9">
+      <c r="A17" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="12">
         <v>4</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="12">
         <v>231</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="12">
         <v>310</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="13">
         <v>685</v>
       </c>
-      <c r="G17" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H17" s="11">
+      <c r="G17" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H17" s="14">
         <v>6.9875</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="9">
+      <c r="A18" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="12">
         <v>4</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="12">
         <v>231</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="12">
         <v>309</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="13">
         <v>685</v>
       </c>
-      <c r="G18" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H18" s="11">
+      <c r="G18" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H18" s="14">
         <v>6.9875</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="9">
+      <c r="A19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="12">
         <v>1</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="12">
         <v>-10</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="12">
         <v>110</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="13">
         <v>519.9999389648</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="14">
         <v>3.425</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="9">
+      <c r="A20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="12">
         <v>2</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="12">
         <v>70</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="12">
         <v>190</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="13">
         <v>404</v>
       </c>
-      <c r="G20" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H20" s="11">
+      <c r="G20" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H20" s="14">
         <v>3.475</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="9">
+      <c r="A21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="12">
         <v>2</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="12">
         <v>71</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="12">
         <v>190</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="13">
         <v>405</v>
       </c>
-      <c r="G21" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H21" s="11">
+      <c r="G21" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H21" s="14">
         <v>3.4875</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="9">
+      <c r="A22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="12">
         <v>3</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="12">
         <v>150</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="12">
         <v>270</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="13">
         <v>500.0000305176</v>
       </c>
-      <c r="G22" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H22" s="11">
+      <c r="G22" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H22" s="14">
         <v>4.675</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="9">
+      <c r="A23" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="12">
         <v>3</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="12">
         <v>151</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="12">
         <v>270</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="13">
         <v>500.0000305176</v>
       </c>
-      <c r="G23" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H23" s="11">
+      <c r="G23" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H23" s="14">
         <v>4.675</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="9">
+      <c r="A24" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="12">
         <v>4</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="12">
         <v>230</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="12">
         <v>350</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="13">
         <v>681</v>
       </c>
-      <c r="G24" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H24" s="11">
+      <c r="G24" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H24" s="14">
         <v>6.9375</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="9">
+      <c r="A25" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="12">
         <v>4</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="12">
         <v>231</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="12">
         <v>350</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="13">
         <v>685</v>
       </c>
-      <c r="G25" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H25" s="11">
+      <c r="G25" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H25" s="14">
         <v>6.9875</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="9">
+      <c r="A26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="12">
         <v>2</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="12">
         <v>80</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="12">
         <v>120</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="13">
         <v>451.9999694824</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="14">
         <v>3.425</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="14">
         <v>8.525</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="9">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="12">
         <v>3</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="12">
         <v>160</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="12">
         <v>200</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="13">
         <v>509</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="13">
         <v>573.9999389648</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="14">
         <v>4.7875</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="9">
+      <c r="A28" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="12">
         <v>4</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="12">
         <v>240</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="12">
         <v>280</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="13">
         <v>646</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="13">
         <v>749.9999389648</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="14">
         <v>6.5</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="9">
+      <c r="A29" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="12">
         <v>5</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="12">
         <v>320</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="12">
         <v>360</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="13">
         <v>680.0000610352</v>
       </c>
-      <c r="G29" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H29" s="11">
+      <c r="G29" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H29" s="14">
         <v>6.925</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="9">
+      <c r="A30" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="12">
         <v>2</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="12">
         <v>70</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="12">
         <v>150</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="13">
         <v>496.9999694824</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="14">
         <v>3.425</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" s="9">
+      <c r="A31" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="12">
         <v>2</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="12">
         <v>70</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="12">
         <v>149</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="13">
         <v>492.9999694824</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="14">
         <v>3.425</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="9">
+      <c r="A32" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="12">
         <v>2</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="12">
         <v>71</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="12">
         <v>150</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="13">
         <v>496.9999694824</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="14">
         <v>3.425</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="9">
+      <c r="A33" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="12">
         <v>2</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="12">
         <v>71</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="12">
         <v>149</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="13">
         <v>492.9999694824</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="14">
         <v>3.425</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="9">
+      <c r="A34" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="12">
         <v>3</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="12">
         <v>150</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="12">
         <v>230</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="13">
         <v>493</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="13">
         <v>630.9999389648</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="14">
         <v>4.5875</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="9">
+      <c r="A35" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="12">
         <v>3</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="12">
         <v>150</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="12">
         <v>229</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="13">
         <v>493</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="13">
         <v>626.9999389648</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="14">
         <v>4.5875</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" s="9">
+      <c r="A36" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="12">
         <v>3</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="12">
         <v>151</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="12">
         <v>230</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="13">
         <v>494</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="13">
         <v>630.9999389648</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36" s="14">
         <v>4.6</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="9">
+      <c r="A37" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="12">
         <v>3</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="12">
         <v>151</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="12">
         <v>229</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="13">
         <v>494</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="13">
         <v>626.9999389648</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="14">
         <v>4.6</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" s="9">
+      <c r="A38" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="12">
         <v>4</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="12">
         <v>230</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="12">
         <v>310</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="13">
         <v>627</v>
       </c>
-      <c r="G38" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H38" s="11">
+      <c r="G38" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H38" s="14">
         <v>6.2625</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B39" s="9">
+      <c r="A39" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="12">
         <v>4</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="12">
         <v>230</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="12">
         <v>309</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="13">
         <v>627</v>
       </c>
-      <c r="G39" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H39" s="11">
+      <c r="G39" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H39" s="14">
         <v>6.2625</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="9">
+      <c r="A40" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="12">
         <v>4</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="12">
         <v>231</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="12">
         <v>310</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="13">
         <v>628</v>
       </c>
-      <c r="G40" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H40" s="11">
+      <c r="G40" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H40" s="14">
         <v>6.275</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B41" s="9">
+      <c r="A41" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="12">
         <v>4</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="12">
         <v>231</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="12">
         <v>309</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="13">
         <v>628</v>
       </c>
-      <c r="G41" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H41" s="11">
+      <c r="G41" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H41" s="14">
         <v>6.275</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" s="9">
+      <c r="A42" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="12">
         <v>5</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="12">
         <v>310</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="12">
         <v>390</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="13">
         <v>680.0000610352</v>
       </c>
-      <c r="G42" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H42" s="11">
+      <c r="G42" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H42" s="14">
         <v>6.925</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="9">
+      <c r="A43" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="12">
         <v>5</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="12">
         <v>310</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="12">
         <v>389</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="13">
         <v>680.0000610352</v>
       </c>
-      <c r="G43" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H43" s="11">
+      <c r="G43" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H43" s="14">
         <v>6.925</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" s="9">
+      <c r="A44" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="12">
         <v>5</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="12">
         <v>311</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="12">
         <v>390</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="13">
         <v>680.0000610352</v>
       </c>
-      <c r="G44" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H44" s="11">
+      <c r="G44" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H44" s="14">
         <v>6.925</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B45" s="9">
+      <c r="A45" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="12">
         <v>5</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="12">
         <v>311</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="12">
         <v>389</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="13">
         <v>680.0000610352</v>
       </c>
-      <c r="G45" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H45" s="11">
+      <c r="G45" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H45" s="14">
         <v>6.925</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" s="9">
+      <c r="A46" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="12">
         <v>6</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="12">
         <v>390</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="12">
         <v>470</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="13">
         <v>796</v>
       </c>
-      <c r="G46" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H46" s="11">
+      <c r="G46" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H46" s="14">
         <v>8.375</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" s="9">
+      <c r="A47" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="12">
         <v>6</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="12">
         <v>390</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="12">
         <v>469</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="13">
         <v>796</v>
       </c>
-      <c r="G47" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H47" s="11">
+      <c r="G47" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H47" s="14">
         <v>8.375</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="9">
+      <c r="A48" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="12">
         <v>6</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="12">
         <v>391</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="12">
         <v>470</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="13">
         <v>800</v>
       </c>
-      <c r="G48" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H48" s="11">
+      <c r="G48" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H48" s="14">
         <v>8.425</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B49" s="9">
+      <c r="A49" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="12">
         <v>6</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="12">
         <v>391</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="12">
         <v>469</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="13">
         <v>800</v>
       </c>
-      <c r="G49" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H49" s="11">
+      <c r="G49" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H49" s="14">
         <v>8.425</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50" s="9">
+      <c r="A50" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="12">
         <v>1</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="12">
         <v>-10</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="12">
         <v>110</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="13">
         <v>438.9999694824</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="14">
         <v>3.425</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="14">
         <v>8.3625</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B51" s="9">
+      <c r="A51" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="12">
         <v>2</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="12">
         <v>70</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="12">
         <v>190</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="13">
         <v>557.9999389648</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="14">
         <v>3.425</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" s="9">
+      <c r="A52" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="12">
         <v>2</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="12">
         <v>71</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="12">
         <v>190</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="13">
         <v>400.0000305176</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="13">
         <v>557.9999389648</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="14">
         <v>3.425</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B53" s="9">
+      <c r="A53" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="12">
         <v>3</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="12">
         <v>150</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="12">
         <v>270</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="13">
         <v>493</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="13">
         <v>721.9999389648</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="14">
         <v>4.5875</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" s="9">
+      <c r="A54" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="12">
         <v>3</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="12">
         <v>151</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="12">
         <v>270</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="13">
         <v>494</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="13">
         <v>721.9999389648</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="14">
         <v>4.6</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B55" s="9">
+      <c r="A55" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="12">
         <v>4</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="12">
         <v>230</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="12">
         <v>350</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="13">
         <v>627</v>
       </c>
-      <c r="G55" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H55" s="11">
+      <c r="G55" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H55" s="14">
         <v>6.2625</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B56" s="9">
+      <c r="A56" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="12">
         <v>4</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="12">
         <v>231</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="12">
         <v>350</v>
       </c>
-      <c r="F56" s="10">
+      <c r="F56" s="13">
         <v>628</v>
       </c>
-      <c r="G56" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H56" s="11">
+      <c r="G56" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H56" s="14">
         <v>6.275</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B57" s="9">
+      <c r="A57" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="12">
         <v>5</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="12">
         <v>310</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="12">
         <v>430</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57" s="13">
         <v>680.0000610352</v>
       </c>
-      <c r="G57" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H57" s="14">
         <v>6.925</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B58" s="9">
+      <c r="A58" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="12">
         <v>5</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="12">
         <v>311</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="12">
         <v>430</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="13">
         <v>680.0000610352</v>
       </c>
-      <c r="G58" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H58" s="11">
+      <c r="G58" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H58" s="14">
         <v>6.925</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B59" s="9">
+      <c r="A59" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" s="12">
         <v>6</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="12">
         <v>390</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="12">
         <v>510</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59" s="13">
         <v>796</v>
       </c>
-      <c r="G59" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H59" s="11">
+      <c r="G59" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H59" s="14">
         <v>8.375</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="9">
+      <c r="A60" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" s="12">
         <v>6</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="12">
         <v>391</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="12">
         <v>510</v>
       </c>
-      <c r="F60" s="10">
+      <c r="F60" s="13">
         <v>800</v>
       </c>
-      <c r="G60" s="10">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H60" s="11">
+      <c r="G60" s="13">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H60" s="14">
         <v>8.425</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="14" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2877,1544 +2907,2919 @@
     <col min="1" max="2" width="5.375" customWidth="1"/>
     <col min="3" max="3" width="7.125" customWidth="1"/>
     <col min="4" max="5" width="17.75" customWidth="1"/>
-    <col min="6" max="7" width="20.25" style="1" customWidth="1"/>
-    <col min="8" max="9" width="11.5" style="2" customWidth="1"/>
+    <col min="6" max="7" width="20.25" style="4" customWidth="1"/>
+    <col min="8" max="9" width="11.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="9">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="9">
         <v>0</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="9">
         <v>70</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="10">
         <v>407.9999694824</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="11">
         <v>3.425</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="11">
         <v>7.975</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="9">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="9">
         <v>0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="9">
         <v>69</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="10">
         <v>406.9999694824</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="11">
         <v>3.425</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="11">
         <v>7.9625</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="9">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="9">
         <v>80</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="9">
         <v>150</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="10">
         <v>426</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="10">
         <v>700.9999389648</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="11">
         <v>3.75</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="9">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="9">
         <v>80</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="9">
         <v>149</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="10">
         <v>426</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="10">
         <v>696.9999389648</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="11">
         <v>3.75</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="9">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="9">
         <v>160</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="9">
         <v>230</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="10">
         <v>500.0000305176</v>
       </c>
-      <c r="G6" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="G6" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H6" s="11">
         <v>4.675</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="A7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="9">
         <v>160</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="9">
         <v>229</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="10">
         <v>500.0000305176</v>
       </c>
-      <c r="G7" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H7" s="8">
+      <c r="G7" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H7" s="11">
         <v>4.675</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="A8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="9">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="9">
         <v>240</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="9">
         <v>310</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="10">
         <v>727</v>
       </c>
-      <c r="G8" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="G8" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H8" s="11">
         <v>7.5125</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="A9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="9">
         <v>4</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="9">
         <v>240</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="9">
         <v>309</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="10">
         <v>727</v>
       </c>
-      <c r="G9" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="G9" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H9" s="11">
         <v>7.5125</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9">
         <v>1</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="9">
         <v>-10</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="9">
         <v>150</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="10">
         <v>700.9999389648</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="11">
         <v>3.425</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9">
         <v>1</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="9">
         <v>-10</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="9">
         <v>149</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="10">
         <v>696.9999389648</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="11">
         <v>3.425</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6">
+      <c r="A12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9">
         <v>2</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="9">
         <v>70</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="9">
         <v>230</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="10">
         <v>404</v>
       </c>
-      <c r="G12" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H12" s="11">
         <v>3.475</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6">
+      <c r="A13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9">
         <v>2</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="9">
         <v>70</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="9">
         <v>229</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="10">
         <v>404</v>
       </c>
-      <c r="G13" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="G13" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H13" s="11">
         <v>3.475</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="6">
+      <c r="A14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="9">
         <v>2</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="9">
         <v>71</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="9">
         <v>230</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="10">
         <v>405</v>
       </c>
-      <c r="G14" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="G14" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H14" s="11">
         <v>3.4875</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6">
+      <c r="A15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="9">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="9">
         <v>71</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="9">
         <v>229</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="10">
         <v>405</v>
       </c>
-      <c r="G15" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="G15" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H15" s="11">
         <v>3.4875</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="6">
+      <c r="A16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="9">
         <v>3</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="9">
         <v>150</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="9">
         <v>310</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="10">
         <v>500.0000305176</v>
       </c>
-      <c r="G16" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H16" s="11">
         <v>4.675</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="6">
+      <c r="A17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="9">
         <v>3</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="9">
         <v>150</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="9">
         <v>309</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="10">
         <v>500.0000305176</v>
       </c>
-      <c r="G17" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="G17" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H17" s="11">
         <v>4.675</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="6">
+      <c r="A18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="9">
         <v>3</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="9">
         <v>151</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="9">
         <v>310</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="10">
         <v>500.0000305176</v>
       </c>
-      <c r="G18" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="G18" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H18" s="11">
         <v>4.675</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="6">
+      <c r="A19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="9">
         <v>3</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="9">
         <v>151</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="9">
         <v>309</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="10">
         <v>500.0000305176</v>
       </c>
-      <c r="G19" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="G19" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H19" s="11">
         <v>4.675</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="6">
+      <c r="A20" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9">
         <v>4</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="9">
         <v>230</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="9">
         <v>390</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="10">
         <v>681</v>
       </c>
-      <c r="G20" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H20" s="8">
+      <c r="G20" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H20" s="11">
         <v>6.9375</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="6">
+      <c r="A21" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="9">
         <v>4</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="9">
         <v>230</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="9">
         <v>389</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="10">
         <v>681</v>
       </c>
-      <c r="G21" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H21" s="8">
+      <c r="G21" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H21" s="11">
         <v>6.9375</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="6">
+      <c r="A22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="9">
         <v>4</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="9">
         <v>231</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="9">
         <v>390</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="10">
         <v>685</v>
       </c>
-      <c r="G22" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H22" s="8">
+      <c r="G22" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H22" s="11">
         <v>6.9875</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="6">
+      <c r="A23" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="9">
         <v>4</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="9">
         <v>231</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="9">
         <v>389</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="10">
         <v>685</v>
       </c>
-      <c r="G23" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H23" s="8">
+      <c r="G23" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H23" s="11">
         <v>6.9875</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="6">
+      <c r="A24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="9">
         <v>2</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="9">
         <v>80</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="9">
         <v>150</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="10">
         <v>496.9999694824</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="11">
         <v>3.425</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="6">
+      <c r="A25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="9">
         <v>2</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="9">
         <v>80</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="9">
         <v>149</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="10">
         <v>492.9999694824</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="11">
         <v>3.425</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="6">
+      <c r="A26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="9">
         <v>3</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="9">
         <v>160</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="9">
         <v>230</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="10">
         <v>509</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="10">
         <v>630.9999389648</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="11">
         <v>4.7875</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="6">
+      <c r="A27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="9">
         <v>3</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="9">
         <v>160</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="9">
         <v>229</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="10">
         <v>509</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="10">
         <v>626.9999389648</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="11">
         <v>4.7875</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="6">
+      <c r="A28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="9">
         <v>4</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="9">
         <v>240</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="9">
         <v>310</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="10">
         <v>646</v>
       </c>
-      <c r="G28" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H28" s="8">
+      <c r="G28" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H28" s="11">
         <v>6.5</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="6">
+      <c r="A29" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="9">
         <v>4</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="9">
         <v>240</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="9">
         <v>309</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="10">
         <v>646</v>
       </c>
-      <c r="G29" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H29" s="8">
+      <c r="G29" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H29" s="11">
         <v>6.5</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="6">
+      <c r="A30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="9">
         <v>5</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="9">
         <v>320</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="9">
         <v>390</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="10">
         <v>680.0000610352</v>
       </c>
-      <c r="G30" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H30" s="8">
+      <c r="G30" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H30" s="11">
         <v>6.925</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" s="6">
+      <c r="A31" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="9">
         <v>5</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="9">
         <v>320</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="9">
         <v>389</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="10">
         <v>680.0000610352</v>
       </c>
-      <c r="G31" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H31" s="8">
+      <c r="G31" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H31" s="11">
         <v>6.925</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="6">
+      <c r="A32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="9">
         <v>1</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="9">
         <v>-10</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="9">
         <v>150</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="10">
         <v>496.9999694824</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="11">
         <v>3.425</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="6">
+      <c r="A33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="9">
         <v>1</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="9">
         <v>-10</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="9">
         <v>149</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="10">
         <v>492.9999694824</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="11">
         <v>3.425</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="6">
+      <c r="A34" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="9">
         <v>2</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="9">
         <v>70</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="9">
         <v>230</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="10">
         <v>630.9999389648</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="11">
         <v>3.425</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="6">
+      <c r="A35" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="9">
         <v>2</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="9">
         <v>70</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="9">
         <v>229</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="10">
         <v>626.9999389648</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="11">
         <v>3.425</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" s="6">
+      <c r="A36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="9">
         <v>2</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="9">
         <v>71</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="9">
         <v>230</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="10">
         <v>630.9999389648</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="11">
         <v>3.425</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="6">
+      <c r="A37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="9">
         <v>2</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="9">
         <v>71</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="9">
         <v>229</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="10">
         <v>400.0000305176</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="10">
         <v>626.9999389648</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="11">
         <v>3.425</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" s="6">
+      <c r="A38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="9">
         <v>3</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="9">
         <v>150</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="9">
         <v>310</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="10">
         <v>493</v>
       </c>
-      <c r="G38" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H38" s="8">
+      <c r="G38" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H38" s="11">
         <v>4.5875</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B39" s="6">
+      <c r="A39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="9">
         <v>3</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="9">
         <v>150</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="9">
         <v>309</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="10">
         <v>493</v>
       </c>
-      <c r="G39" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H39" s="8">
+      <c r="G39" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H39" s="11">
         <v>4.5875</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="6">
+      <c r="A40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="9">
         <v>3</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="9">
         <v>151</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="9">
         <v>310</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="10">
         <v>494</v>
       </c>
-      <c r="G40" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H40" s="8">
+      <c r="G40" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H40" s="11">
         <v>4.6</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B41" s="6">
+      <c r="A41" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="9">
         <v>3</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="9">
         <v>151</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="9">
         <v>309</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="10">
         <v>494</v>
       </c>
-      <c r="G41" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H41" s="8">
+      <c r="G41" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H41" s="11">
         <v>4.6</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="I41" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" s="6">
+      <c r="A42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="9">
         <v>4</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="9">
         <v>230</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="9">
         <v>390</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="10">
         <v>627</v>
       </c>
-      <c r="G42" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H42" s="8">
+      <c r="G42" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H42" s="11">
         <v>6.2625</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="6">
+      <c r="A43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="9">
         <v>4</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="9">
         <v>230</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="9">
         <v>389</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="10">
         <v>627</v>
       </c>
-      <c r="G43" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H43" s="8">
+      <c r="G43" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H43" s="11">
         <v>6.2625</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="I43" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" s="6">
+      <c r="A44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="9">
         <v>4</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="9">
         <v>231</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="9">
         <v>390</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="10">
         <v>628</v>
       </c>
-      <c r="G44" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H44" s="8">
+      <c r="G44" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H44" s="11">
         <v>6.275</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="I44" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B45" s="6">
+      <c r="A45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="9">
         <v>4</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="9">
         <v>231</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="9">
         <v>389</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="10">
         <v>628</v>
       </c>
-      <c r="G45" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H45" s="8">
+      <c r="G45" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H45" s="11">
         <v>6.275</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="I45" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" s="6">
+      <c r="A46" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="9">
         <v>5</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="9">
         <v>310</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="9">
         <v>470</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="10">
         <v>680.0000610352</v>
       </c>
-      <c r="G46" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H46" s="8">
+      <c r="G46" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H46" s="11">
         <v>6.925</v>
       </c>
-      <c r="I46" s="8" t="s">
+      <c r="I46" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" s="6">
+      <c r="A47" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="9">
         <v>5</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="9">
         <v>310</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="9">
         <v>469</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="10">
         <v>680.0000610352</v>
       </c>
-      <c r="G47" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H47" s="8">
+      <c r="G47" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H47" s="11">
         <v>6.925</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="I47" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="6">
+      <c r="A48" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="9">
         <v>5</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="9">
         <v>311</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="9">
         <v>470</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="10">
         <v>680.0000610352</v>
       </c>
-      <c r="G48" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H48" s="8">
+      <c r="G48" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H48" s="11">
         <v>6.925</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I48" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B49" s="6">
+      <c r="A49" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="9">
         <v>5</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="9">
         <v>311</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="9">
         <v>469</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="10">
         <v>680.0000610352</v>
       </c>
-      <c r="G49" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H49" s="8">
+      <c r="G49" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H49" s="11">
         <v>6.925</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="I49" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50" s="6">
+      <c r="A50" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="9">
         <v>6</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="9">
         <v>390</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E50" s="9">
         <v>550</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="10">
         <v>796</v>
       </c>
-      <c r="G50" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H50" s="8">
+      <c r="G50" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H50" s="11">
         <v>8.375</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="I50" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B51" s="6">
+      <c r="A51" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="9">
         <v>6</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="9">
         <v>390</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="9">
         <v>549</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="10">
         <v>796</v>
       </c>
-      <c r="G51" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H51" s="8">
+      <c r="G51" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H51" s="11">
         <v>8.375</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="I51" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" s="6">
+      <c r="A52" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="9">
         <v>6</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="9">
         <v>391</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="9">
         <v>550</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="10">
         <v>800</v>
       </c>
-      <c r="G52" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H52" s="8">
+      <c r="G52" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H52" s="11">
         <v>8.425</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="I52" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B53" s="6">
+      <c r="A53" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="9">
         <v>6</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="9">
         <v>391</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="9">
         <v>549</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="10">
         <v>800</v>
       </c>
-      <c r="G53" s="7">
-        <v>817.9999389648</v>
-      </c>
-      <c r="H53" s="8">
+      <c r="G53" s="10">
+        <v>817.9999389648</v>
+      </c>
+      <c r="H53" s="11">
         <v>8.425</v>
       </c>
-      <c r="I53" s="8" t="s">
+      <c r="I53" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="3" width="5.375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="17.75" style="1" customWidth="1"/>
+    <col min="6" max="7" width="24.75" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:7">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3">
+        <v>101</v>
+      </c>
+      <c r="E2" s="3">
+        <v>764</v>
+      </c>
+      <c r="F2" s="3">
+        <v>489.9999694824</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="3">
+        <v>181</v>
+      </c>
+      <c r="E3" s="3">
+        <v>764</v>
+      </c>
+      <c r="F3" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3">
+        <v>261</v>
+      </c>
+      <c r="E4" s="3">
+        <v>764</v>
+      </c>
+      <c r="F4" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3">
+        <v>341</v>
+      </c>
+      <c r="E5" s="3">
+        <v>764</v>
+      </c>
+      <c r="F5" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3">
+        <v>421</v>
+      </c>
+      <c r="E6" s="3">
+        <v>764</v>
+      </c>
+      <c r="F6" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3">
+        <v>501</v>
+      </c>
+      <c r="E7" s="3">
+        <v>764</v>
+      </c>
+      <c r="F7" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3">
+        <v>581</v>
+      </c>
+      <c r="E8" s="3">
+        <v>764</v>
+      </c>
+      <c r="F8" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3">
+        <v>661</v>
+      </c>
+      <c r="E9" s="3">
+        <v>764</v>
+      </c>
+      <c r="F9" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>164</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3">
+        <v>500.0000305176</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>244</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3">
+        <v>122</v>
+      </c>
+      <c r="E12" s="3">
+        <v>404</v>
+      </c>
+      <c r="F12" s="3">
+        <v>561.9999389648</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="3">
+        <v>202</v>
+      </c>
+      <c r="E13" s="3">
+        <v>484</v>
+      </c>
+      <c r="F13" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="3">
+        <v>282</v>
+      </c>
+      <c r="E14" s="3">
+        <v>564</v>
+      </c>
+      <c r="F14" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="3">
+        <v>362</v>
+      </c>
+      <c r="E15" s="3">
+        <v>644</v>
+      </c>
+      <c r="F15" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="3">
+        <v>442</v>
+      </c>
+      <c r="E16" s="3">
+        <v>724</v>
+      </c>
+      <c r="F16" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="3">
+        <v>522</v>
+      </c>
+      <c r="E17" s="3">
+        <v>764</v>
+      </c>
+      <c r="F17" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:7">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="3">
+        <v>102</v>
+      </c>
+      <c r="E18" s="3">
+        <v>484</v>
+      </c>
+      <c r="F18" s="3">
+        <v>493.9999694824</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3">
+        <v>3</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="3">
+        <v>182</v>
+      </c>
+      <c r="E19" s="3">
+        <v>564</v>
+      </c>
+      <c r="F19" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="3">
+        <v>262</v>
+      </c>
+      <c r="E20" s="3">
+        <v>644</v>
+      </c>
+      <c r="F20" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3">
+        <v>5</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="3">
+        <v>342</v>
+      </c>
+      <c r="E21" s="3">
+        <v>724</v>
+      </c>
+      <c r="F21" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3">
+        <v>6</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="3">
+        <v>422</v>
+      </c>
+      <c r="E22" s="3">
+        <v>764</v>
+      </c>
+      <c r="F22" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:7">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="3">
+        <v>502</v>
+      </c>
+      <c r="E23" s="3">
+        <v>764</v>
+      </c>
+      <c r="F23" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:7">
+      <c r="A24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="3">
+        <v>8</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="3">
+        <v>582</v>
+      </c>
+      <c r="E24" s="3">
+        <v>764</v>
+      </c>
+      <c r="F24" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="3">
+        <v>9</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="3">
+        <v>662</v>
+      </c>
+      <c r="E25" s="3">
+        <v>764</v>
+      </c>
+      <c r="F25" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:7">
+      <c r="A26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>54</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="3">
+        <v>400.0000305176</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:7">
+      <c r="A27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="3">
+        <v>62</v>
+      </c>
+      <c r="E27" s="3">
+        <v>134</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="3">
+        <v>500.0000305176</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:7">
+      <c r="A28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="3">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="3">
+        <v>142</v>
+      </c>
+      <c r="E28" s="3">
+        <v>214</v>
+      </c>
+      <c r="F28" s="3">
+        <v>653.9999389648</v>
+      </c>
+      <c r="G28" s="3">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:7">
+      <c r="A29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="3">
+        <v>222</v>
+      </c>
+      <c r="E29" s="3">
+        <v>294</v>
+      </c>
+      <c r="F29" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:7">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="3">
+        <v>302</v>
+      </c>
+      <c r="E30" s="3">
+        <v>374</v>
+      </c>
+      <c r="F30" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3">
+        <v>6</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="3">
+        <v>382</v>
+      </c>
+      <c r="E31" s="3">
+        <v>454</v>
+      </c>
+      <c r="F31" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3">
+        <v>7</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="3">
+        <v>462</v>
+      </c>
+      <c r="E32" s="3">
+        <v>534</v>
+      </c>
+      <c r="F32" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="3">
+        <v>8</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="3">
+        <v>542</v>
+      </c>
+      <c r="E33" s="3">
+        <v>614</v>
+      </c>
+      <c r="F33" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:7">
+      <c r="A34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="3">
+        <v>9</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="3">
+        <v>622</v>
+      </c>
+      <c r="E34" s="3">
+        <v>694</v>
+      </c>
+      <c r="F34" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:7">
+      <c r="A35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="3">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="3">
+        <v>101</v>
+      </c>
+      <c r="E35" s="3">
+        <v>764</v>
+      </c>
+      <c r="F35" s="3">
+        <v>426.9999694824</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:7">
+      <c r="A36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="3">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="3">
+        <v>181</v>
+      </c>
+      <c r="E36" s="3">
+        <v>764</v>
+      </c>
+      <c r="F36" s="3">
+        <v>542.9999389648</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:7">
+      <c r="A37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="3">
+        <v>4</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="3">
+        <v>261</v>
+      </c>
+      <c r="E37" s="3">
+        <v>764</v>
+      </c>
+      <c r="F37" s="3">
+        <v>697.9999389648</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:7">
+      <c r="A38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="3">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="3">
+        <v>341</v>
+      </c>
+      <c r="E38" s="3">
+        <v>764</v>
+      </c>
+      <c r="F38" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:7">
+      <c r="A39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="3">
+        <v>6</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="3">
+        <v>421</v>
+      </c>
+      <c r="E39" s="3">
+        <v>764</v>
+      </c>
+      <c r="F39" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:7">
+      <c r="A40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="3">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="3">
+        <v>501</v>
+      </c>
+      <c r="E40" s="3">
+        <v>764</v>
+      </c>
+      <c r="F40" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:7">
+      <c r="A41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="3">
+        <v>8</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="3">
+        <v>581</v>
+      </c>
+      <c r="E41" s="3">
+        <v>764</v>
+      </c>
+      <c r="F41" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:7">
+      <c r="A42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="3">
+        <v>9</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="3">
+        <v>661</v>
+      </c>
+      <c r="E42" s="3">
+        <v>764</v>
+      </c>
+      <c r="F42" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:7">
+      <c r="A43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>164</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:7">
+      <c r="A44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>244</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="3">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:7">
+      <c r="A45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="3">
+        <v>3</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="3">
+        <v>42</v>
+      </c>
+      <c r="E45" s="3">
+        <v>324</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" s="3">
+        <v>680.0000610352</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:7">
+      <c r="A46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="3">
+        <v>4</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="3">
+        <v>122</v>
+      </c>
+      <c r="E46" s="3">
+        <v>404</v>
+      </c>
+      <c r="F46" s="3">
+        <v>456.9999694824</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:7">
+      <c r="A47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="3">
+        <v>5</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="3">
+        <v>202</v>
+      </c>
+      <c r="E47" s="3">
+        <v>484</v>
+      </c>
+      <c r="F47" s="3">
+        <v>578.9999389648</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:7">
+      <c r="A48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="3">
+        <v>6</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="3">
+        <v>282</v>
+      </c>
+      <c r="E48" s="3">
+        <v>564</v>
+      </c>
+      <c r="F48" s="3">
+        <v>754.9999389648</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:7">
+      <c r="A49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="3">
+        <v>7</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="3">
+        <v>362</v>
+      </c>
+      <c r="E49" s="3">
+        <v>644</v>
+      </c>
+      <c r="F49" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:7">
+      <c r="A50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="3">
+        <v>8</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="3">
+        <v>442</v>
+      </c>
+      <c r="E50" s="3">
+        <v>724</v>
+      </c>
+      <c r="F50" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:7">
+      <c r="A51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="3">
+        <v>9</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="3">
+        <v>522</v>
+      </c>
+      <c r="E51" s="3">
+        <v>764</v>
+      </c>
+      <c r="F51" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:7">
+      <c r="A52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="3">
+        <v>2</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="3">
+        <v>102</v>
+      </c>
+      <c r="E52" s="3">
+        <v>484</v>
+      </c>
+      <c r="F52" s="3">
+        <v>427.9999694824</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="1:7">
+      <c r="A53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="3">
+        <v>3</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="3">
+        <v>182</v>
+      </c>
+      <c r="E53" s="3">
+        <v>564</v>
+      </c>
+      <c r="F53" s="3">
+        <v>543.9999389648</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:7">
+      <c r="A54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="3">
+        <v>4</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="3">
+        <v>262</v>
+      </c>
+      <c r="E54" s="3">
+        <v>644</v>
+      </c>
+      <c r="F54" s="3">
+        <v>701.9999389648</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:7">
+      <c r="A55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="3">
+        <v>5</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="3">
+        <v>342</v>
+      </c>
+      <c r="E55" s="3">
+        <v>724</v>
+      </c>
+      <c r="F55" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:7">
+      <c r="A56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="3">
+        <v>6</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="3">
+        <v>422</v>
+      </c>
+      <c r="E56" s="3">
+        <v>764</v>
+      </c>
+      <c r="F56" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:7">
+      <c r="A57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="3">
+        <v>7</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="3">
+        <v>502</v>
+      </c>
+      <c r="E57" s="3">
+        <v>764</v>
+      </c>
+      <c r="F57" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:7">
+      <c r="A58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="3">
+        <v>8</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D58" s="3">
+        <v>582</v>
+      </c>
+      <c r="E58" s="3">
+        <v>764</v>
+      </c>
+      <c r="F58" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:7">
+      <c r="A59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" s="3">
+        <v>9</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" s="3">
+        <v>662</v>
+      </c>
+      <c r="E59" s="3">
+        <v>764</v>
+      </c>
+      <c r="F59" s="3">
+        <v>817.9999389648</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
